--- a/財務/個人資產負債表.xlsx
+++ b/財務/個人資產負債表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="資產負債表_快照" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="收支摘要" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="月度追蹤_2026" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="年度追蹤" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資產負債表_快照" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="收支摘要" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度追蹤_2026" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="年度追蹤" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1106,7 +1106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="B19" s="6" t="n"/>
       <c r="C19" s="10" t="n">
-        <v>19200</v>
+        <v>29560</v>
       </c>
       <c r="D19" s="26" t="inlineStr">
         <is>
@@ -1468,6 +1468,11 @@
         </is>
       </c>
       <c r="E19" s="6" t="n"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kling 895/月 + 其他；已移除 Vllo 380/年</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
